--- a/docs/MATRIZ_CC_REGLAS_MOVIMIENTOS.xlsx
+++ b/docs/MATRIZ_CC_REGLAS_MOVIMIENTOS.xlsx
@@ -415,7 +415,7 @@
         <v>Generado (UTC)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-28T17:47:53.500Z</v>
+        <v>2026-05-18T13:13:06.801Z</v>
       </c>
     </row>
     <row r="4">
